--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T10:55:45+00:00</t>
+    <t>2023-04-05T15:18:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:18:36+00:00</t>
+    <t>2023-04-05T15:41:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:41:27+00:00</t>
+    <t>2023-04-05T15:52:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:52:08+00:00</t>
+    <t>2023-04-05T15:53:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -656,7 +656,7 @@
     <t>Location.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/fr-address-extended}
+    <t xml:space="preserve">Address {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-address-extended}
 </t>
   </si>
   <si>
@@ -1248,7 +1248,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="93.3046875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="106.27734375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:53:16+00:00</t>
+    <t>2023-04-05T15:55:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:55:13+00:00</t>
+    <t>2023-04-05T16:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:00:25+00:00</t>
+    <t>2023-04-05T16:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:20:25+00:00</t>
+    <t>2023-04-05T16:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:21:30+00:00</t>
+    <t>2023-04-05T16:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:24:37+00:00</t>
+    <t>2023-04-05T17:39:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T17:39:15+00:00</t>
+    <t>2023-04-07T12:42:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil créé à partir de la ressource Location dans le contexte de l'Annuaire Santé pour prise en compte de l'adresse du professionnel au niveau du profil AsPractitionerRole.</t>
+    <t>Profil créé à partir de la ressource Location dans le contexte de l'Annuaire Santé pour prise en compte de l'adresse du professionnel au niveau du profil AsPractitionerRoleProfile.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-07T12:42:40+00:00</t>
+    <t>2023-04-12T10:00:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T10:00:48+00:00</t>
+    <t>2023-04-12T10:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T10:05:52+00:00</t>
+    <t>2023-04-12T10:08:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T10:08:35+00:00</t>
+    <t>2023-04-12T14:03:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T14:03:54+00:00</t>
+    <t>2023-04-13T07:49:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T07:49:09+00:00</t>
+    <t>2023-04-13T08:12:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:12:13+00:00</t>
+    <t>2023-04-13T08:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:22:34+00:00</t>
+    <t>2023-04-13T08:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:33:21+00:00</t>
+    <t>2023-04-13T08:34:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:34:34+00:00</t>
+    <t>2023-04-13T08:54:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:54:00+00:00</t>
+    <t>2023-04-13T09:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T09:51:53+00:00</t>
+    <t>2023-04-13T10:21:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T10:21:56+00:00</t>
+    <t>2023-04-13T12:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T12:58:26+00:00</t>
+    <t>2023-04-13T15:00:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T15:00:08+00:00</t>
+    <t>2023-04-13T15:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T15:16:05+00:00</t>
+    <t>2023-04-14T12:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T12:31:23+00:00</t>
+    <t>2023-04-14T12:45:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T12:45:28+00:00</t>
+    <t>2023-04-14T13:02:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T13:02:26+00:00</t>
+    <t>2023-04-14T13:12:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T13:12:31+00:00</t>
+    <t>2023-04-17T08:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:15:24+00:00</t>
+    <t>2023-04-17T08:17:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:17:23+00:00</t>
+    <t>2023-04-17T08:37:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:37:32+00:00</t>
+    <t>2023-04-17T09:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T09:07:20+00:00</t>
+    <t>2023-04-17T10:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T10:39:40+00:00</t>
+    <t>2023-04-17T10:56:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T10:56:20+00:00</t>
+    <t>2023-04-17T11:14:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:14:19+00:00</t>
+    <t>2023-04-17T11:17:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:17:21+00:00</t>
+    <t>2023-04-17T11:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:39:02+00:00</t>
+    <t>2023-04-17T11:54:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:54:58+00:00</t>
+    <t>2023-04-17T12:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T12:02:32+00:00</t>
+    <t>2023-04-17T13:37:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T13:37:35+00:00</t>
+    <t>2023-04-17T14:05:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T14:05:09+00:00</t>
+    <t>2023-04-20T17:39:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:39:34+00:00</t>
+    <t>2023-04-20T17:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:42:03+00:00</t>
+    <t>2023-04-20T17:43:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:43:10+00:00</t>
+    <t>2023-04-20T17:43:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:43:52+00:00</t>
+    <t>2023-04-28T11:09:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:09:12+00:00</t>
+    <t>2023-04-28T15:03:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T15:03:41+00:00</t>
+    <t>2023-04-28T18:35:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:35:22+00:00</t>
+    <t>2023-04-28T18:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:37:07+00:00</t>
+    <t>2023-04-28T18:58:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:58:16+00:00</t>
+    <t>2023-05-02T06:31:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T06:31:09+00:00</t>
+    <t>2023-05-02T06:34:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T06:34:44+00:00</t>
+    <t>2023-05-02T07:22:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T07:22:02+00:00</t>
+    <t>2023-05-02T14:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:04:27+00:00</t>
+    <t>2023-05-02T14:10:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:10:11+00:00</t>
+    <t>2023-05-02T14:20:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:20:51+00:00</t>
+    <t>2023-05-02T14:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:32:14+00:00</t>
+    <t>2023-05-02T15:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T15:50:41+00:00</t>
+    <t>2023-05-02T16:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T16:15:55+00:00</t>
+    <t>2023-05-02T17:25:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:25:18+00:00</t>
+    <t>2023-05-02T17:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:45:11+00:00</t>
+    <t>2023-05-02T17:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:46:32+00:00</t>
+    <t>2023-05-04T14:01:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:01:59+00:00</t>
+    <t>2023-05-04T14:04:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:04:48+00:00</t>
+    <t>2023-05-04T14:08:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:08:50+00:00</t>
+    <t>2023-05-05T17:21:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
